--- a/data/catalog/routing.xlsx
+++ b/data/catalog/routing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4798" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4685" uniqueCount="1180">
   <si>
     <t>family</t>
   </si>
@@ -3230,7 +3230,7 @@
     <t>P-LTEA-EA</t>
   </si>
   <si>
-    <t>https://cisco.com/site/us/en/products/networking/sdwan-routers/catalyst-8300-series-platforms/interfaces-modules/index.html</t>
+    <t>https://www.cisco.com/site/us/en/products/networking/sdwan-routers/catalyst-8300-series-platforms/interfaces-modules/index.html</t>
   </si>
   <si>
     <t>router-modules.csv row 2</t>
@@ -3245,7 +3245,7 @@
     <t>P-LTEA7-EAL</t>
   </si>
   <si>
-    <t>https://cisco.com/c/en/us/solutions/collateral/enterprise-networks/4g-lte-solutions/datasheet-c78-743503.html</t>
+    <t>https://www.cisco.com/c/en/us/solutions/collateral/enterprise-networks/4g-lte-solutions/datasheet-c78-743503.html</t>
   </si>
   <si>
     <t>router-modules.csv row 3</t>
@@ -3269,7 +3269,7 @@
     <t>LTE Pluggable</t>
   </si>
   <si>
-    <t>https://cisco.com/c/en/us/products/collateral/routers/1000-series-integrated-services-routers-isr/1kseries-integrated-services-routers-guide.html</t>
+    <t>https://www.cisco.com/c/en/us/products/collateral/routers/1000-series-integrated-services-routers-isr/1kseries-integrated-services-routers-guide.html</t>
   </si>
   <si>
     <t>router-modules.csv row 5</t>
@@ -3284,7 +3284,7 @@
     <t>C-SM-16P4M2X</t>
   </si>
   <si>
-    <t>https://cisco.com/c/en/us/products/collateral/routers/catalyst-8300-series-edge-platforms/catalyst-8000-sm-switch-module-ds.html</t>
+    <t>https://www.cisco.com/c/en/us/products/collateral/routers/catalyst-8300-series-edge-platforms/catalyst-8000-sm-switch-module-ds.html</t>
   </si>
   <si>
     <t>router-modules.csv row 6</t>
@@ -3323,7 +3323,7 @@
     <t>C-NIM-8M</t>
   </si>
   <si>
-    <t>https://cisco.com/c/en/us/products/collateral/routers/catalyst-8300-series-edge-platforms/catalyst-8000-series-gigabit-ethernet-lan-wan-modules-ds.html</t>
+    <t>https://www.cisco.com/c/en/us/products/collateral/routers/catalyst-8300-series-edge-platforms/catalyst-8000-series-gigabit-ethernet-lan-wan-modules-ds.html</t>
   </si>
   <si>
     <t>router-modules.csv row 9</t>
@@ -3413,7 +3413,7 @@
     <t>A900-IMA8S</t>
   </si>
   <si>
-    <t>https://cisco.com/c/en/us/td/docs/routers/asr903/release/notes/17-12-1/b-rn-xe-17-12-x-asr900/m-intro-17-12-x-asr900.html</t>
+    <t>https://www.cisco.com/c/en/us/td/docs/routers/asr903/release/notes/17-12-1/b-rn-xe-17-12-x-asr900/m-intro-17-12-x-asr900.html</t>
   </si>
   <si>
     <t>router-modules.csv row 17</t>
@@ -5187,9 +5187,6 @@
       <c r="AQ2">
         <v>4</v>
       </c>
-      <c r="AV2" t="s">
-        <v>286</v>
-      </c>
       <c r="AW2" t="s">
         <v>288</v>
       </c>
@@ -5290,9 +5287,6 @@
       <c r="AQ3">
         <v>6</v>
       </c>
-      <c r="AV3" t="s">
-        <v>286</v>
-      </c>
       <c r="AW3" t="s">
         <v>288</v>
       </c>
@@ -5393,9 +5387,6 @@
       <c r="AQ4">
         <v>16</v>
       </c>
-      <c r="AV4" t="s">
-        <v>286</v>
-      </c>
       <c r="AW4" t="s">
         <v>288</v>
       </c>
@@ -5496,9 +5487,6 @@
       <c r="AQ5">
         <v>14</v>
       </c>
-      <c r="AV5" t="s">
-        <v>286</v>
-      </c>
       <c r="AW5" t="s">
         <v>288</v>
       </c>
@@ -5596,9 +5584,6 @@
       <c r="AP6">
         <v>0</v>
       </c>
-      <c r="AV6" t="s">
-        <v>286</v>
-      </c>
       <c r="AW6" t="s">
         <v>288</v>
       </c>
@@ -5690,9 +5675,6 @@
       <c r="AP7">
         <v>0</v>
       </c>
-      <c r="AV7" t="s">
-        <v>286</v>
-      </c>
       <c r="AX7" s="1" t="s">
         <v>308</v>
       </c>
@@ -5879,9 +5861,6 @@
       <c r="AQ9">
         <v>1</v>
       </c>
-      <c r="AV9" t="s">
-        <v>286</v>
-      </c>
       <c r="AX9" s="1" t="s">
         <v>316</v>
       </c>
@@ -5968,9 +5947,6 @@
       <c r="AP10">
         <v>0</v>
       </c>
-      <c r="AV10" t="s">
-        <v>286</v>
-      </c>
       <c r="AX10" s="1" t="s">
         <v>319</v>
       </c>
@@ -6057,9 +6033,6 @@
       <c r="AP11">
         <v>0</v>
       </c>
-      <c r="AV11" t="s">
-        <v>286</v>
-      </c>
       <c r="AX11" s="1" t="s">
         <v>322</v>
       </c>
@@ -6146,9 +6119,6 @@
       <c r="AP12">
         <v>0</v>
       </c>
-      <c r="AV12" t="s">
-        <v>286</v>
-      </c>
       <c r="AX12" s="1" t="s">
         <v>325</v>
       </c>
@@ -6264,9 +6234,6 @@
       <c r="AU13">
         <v>2500</v>
       </c>
-      <c r="AV13" t="s">
-        <v>286</v>
-      </c>
       <c r="AW13" t="s">
         <v>334</v>
       </c>
@@ -6385,9 +6352,6 @@
       <c r="AU14">
         <v>1500</v>
       </c>
-      <c r="AV14" t="s">
-        <v>286</v>
-      </c>
       <c r="AW14" t="s">
         <v>341</v>
       </c>
@@ -6507,9 +6471,6 @@
       <c r="AU15">
         <v>6000</v>
       </c>
-      <c r="AV15" t="s">
-        <v>286</v>
-      </c>
       <c r="AW15" t="s">
         <v>349</v>
       </c>
@@ -6627,9 +6588,6 @@
       <c r="AU16">
         <v>6000</v>
       </c>
-      <c r="AV16" t="s">
-        <v>286</v>
-      </c>
       <c r="AW16" t="s">
         <v>349</v>
       </c>
@@ -6748,9 +6706,6 @@
       <c r="AU17">
         <v>6000</v>
       </c>
-      <c r="AV17" t="s">
-        <v>286</v>
-      </c>
       <c r="AW17" t="s">
         <v>349</v>
       </c>
@@ -6867,9 +6822,6 @@
       <c r="AU18">
         <v>6000</v>
       </c>
-      <c r="AV18" t="s">
-        <v>286</v>
-      </c>
       <c r="AW18" t="s">
         <v>349</v>
       </c>
@@ -6984,9 +6936,6 @@
       <c r="AU19">
         <v>10000</v>
       </c>
-      <c r="AV19" t="s">
-        <v>286</v>
-      </c>
       <c r="AW19" t="s">
         <v>372</v>
       </c>
@@ -7103,9 +7052,6 @@
       <c r="AU20">
         <v>10000</v>
       </c>
-      <c r="AV20" t="s">
-        <v>286</v>
-      </c>
       <c r="AW20" t="s">
         <v>372</v>
       </c>
@@ -7222,9 +7168,6 @@
       <c r="AU21">
         <v>10000</v>
       </c>
-      <c r="AV21" t="s">
-        <v>286</v>
-      </c>
       <c r="AW21" t="s">
         <v>372</v>
       </c>
@@ -7340,9 +7283,6 @@
       </c>
       <c r="AU22">
         <v>8000</v>
-      </c>
-      <c r="AV22" t="s">
-        <v>286</v>
       </c>
       <c r="AW22" t="s">
         <v>372</v>
@@ -7428,9 +7368,6 @@
       <c r="AQ23">
         <v>0</v>
       </c>
-      <c r="AV23" t="s">
-        <v>286</v>
-      </c>
       <c r="AW23" t="s">
         <v>393</v>
       </c>
@@ -7540,9 +7477,6 @@
       <c r="AU24">
         <v>250</v>
       </c>
-      <c r="AV24" t="s">
-        <v>286</v>
-      </c>
       <c r="AW24" t="s">
         <v>402</v>
       </c>
@@ -7652,9 +7586,6 @@
       <c r="AU25">
         <v>250</v>
       </c>
-      <c r="AV25" t="s">
-        <v>286</v>
-      </c>
       <c r="AW25" t="s">
         <v>402</v>
       </c>
@@ -7764,9 +7695,6 @@
       <c r="AU26">
         <v>250</v>
       </c>
-      <c r="AV26" t="s">
-        <v>286</v>
-      </c>
       <c r="AW26" t="s">
         <v>402</v>
       </c>
@@ -7873,9 +7801,6 @@
       <c r="AT27">
         <v>1500</v>
       </c>
-      <c r="AV27" t="s">
-        <v>286</v>
-      </c>
       <c r="AW27" t="s">
         <v>402</v>
       </c>
@@ -7985,9 +7910,6 @@
       <c r="AU28">
         <v>250</v>
       </c>
-      <c r="AV28" t="s">
-        <v>286</v>
-      </c>
       <c r="AW28" t="s">
         <v>402</v>
       </c>
@@ -8097,9 +8019,6 @@
       <c r="AU29">
         <v>250</v>
       </c>
-      <c r="AV29" t="s">
-        <v>286</v>
-      </c>
       <c r="AW29" t="s">
         <v>402</v>
       </c>
@@ -8212,9 +8131,6 @@
       <c r="AU30">
         <v>250</v>
       </c>
-      <c r="AV30" t="s">
-        <v>286</v>
-      </c>
       <c r="AW30" t="s">
         <v>427</v>
       </c>
@@ -8327,9 +8243,6 @@
       <c r="AU31">
         <v>250</v>
       </c>
-      <c r="AV31" t="s">
-        <v>286</v>
-      </c>
       <c r="AW31" t="s">
         <v>427</v>
       </c>
@@ -8442,9 +8355,6 @@
       <c r="AU32">
         <v>250</v>
       </c>
-      <c r="AV32" t="s">
-        <v>286</v>
-      </c>
       <c r="AW32" t="s">
         <v>427</v>
       </c>
@@ -8554,9 +8464,6 @@
       <c r="AT33">
         <v>1000</v>
       </c>
-      <c r="AV33" t="s">
-        <v>286</v>
-      </c>
       <c r="AW33" t="s">
         <v>427</v>
       </c>
@@ -9108,9 +9015,6 @@
       <c r="AQ38">
         <v>0</v>
       </c>
-      <c r="AV38" t="s">
-        <v>286</v>
-      </c>
       <c r="AW38" t="s">
         <v>465</v>
       </c>
@@ -9211,9 +9115,6 @@
       <c r="AQ39">
         <v>0</v>
       </c>
-      <c r="AV39" t="s">
-        <v>286</v>
-      </c>
       <c r="AW39" t="s">
         <v>465</v>
       </c>
@@ -9314,9 +9215,6 @@
       <c r="AQ40">
         <v>0</v>
       </c>
-      <c r="AV40" t="s">
-        <v>286</v>
-      </c>
       <c r="AW40" t="s">
         <v>465</v>
       </c>
@@ -9417,9 +9315,6 @@
       <c r="AQ41">
         <v>0</v>
       </c>
-      <c r="AV41" t="s">
-        <v>286</v>
-      </c>
       <c r="AW41" t="s">
         <v>465</v>
       </c>
@@ -10320,9 +10215,6 @@
       <c r="AU49">
         <v>3500</v>
       </c>
-      <c r="AV49" t="s">
-        <v>286</v>
-      </c>
       <c r="AW49" t="s">
         <v>520</v>
       </c>
@@ -10432,9 +10324,6 @@
       <c r="AU50">
         <v>2000</v>
       </c>
-      <c r="AV50" t="s">
-        <v>286</v>
-      </c>
       <c r="AW50" t="s">
         <v>520</v>
       </c>
@@ -10541,9 +10430,6 @@
       <c r="AU51">
         <v>10000</v>
       </c>
-      <c r="AV51" t="s">
-        <v>286</v>
-      </c>
       <c r="AW51" t="s">
         <v>520</v>
       </c>
@@ -10653,9 +10539,6 @@
       <c r="AU52">
         <v>10000</v>
       </c>
-      <c r="AV52" t="s">
-        <v>286</v>
-      </c>
       <c r="AW52" t="s">
         <v>520</v>
       </c>
@@ -10765,9 +10648,6 @@
       <c r="AU53">
         <v>10000</v>
       </c>
-      <c r="AV53" t="s">
-        <v>286</v>
-      </c>
       <c r="AW53" t="s">
         <v>520</v>
       </c>
@@ -10868,9 +10748,6 @@
       <c r="AQ54">
         <v>0</v>
       </c>
-      <c r="AV54" t="s">
-        <v>286</v>
-      </c>
       <c r="AW54" t="s">
         <v>520</v>
       </c>
@@ -10983,9 +10860,6 @@
       <c r="AU55">
         <v>250</v>
       </c>
-      <c r="AV55" t="s">
-        <v>286</v>
-      </c>
       <c r="AW55" t="s">
         <v>554</v>
       </c>
@@ -11099,9 +10973,6 @@
       <c r="AU56">
         <v>250</v>
       </c>
-      <c r="AV56" t="s">
-        <v>286</v>
-      </c>
       <c r="AW56" t="s">
         <v>560</v>
       </c>
@@ -11212,9 +11083,6 @@
       <c r="AU57">
         <v>1500</v>
       </c>
-      <c r="AV57" t="s">
-        <v>286</v>
-      </c>
       <c r="AW57" t="s">
         <v>554</v>
       </c>
@@ -11322,9 +11190,6 @@
       <c r="AU58">
         <v>500</v>
       </c>
-      <c r="AV58" t="s">
-        <v>286</v>
-      </c>
       <c r="AW58" t="s">
         <v>568</v>
       </c>
@@ -11432,9 +11297,6 @@
       <c r="AU59">
         <v>3000</v>
       </c>
-      <c r="AV59" t="s">
-        <v>286</v>
-      </c>
       <c r="AW59" t="s">
         <v>568</v>
       </c>
@@ -11545,9 +11407,6 @@
       <c r="AS60">
         <v>450</v>
       </c>
-      <c r="AV60" t="s">
-        <v>286</v>
-      </c>
       <c r="AW60" t="s">
         <v>554</v>
       </c>
@@ -11661,9 +11520,6 @@
       <c r="AS61">
         <v>450</v>
       </c>
-      <c r="AV61" t="s">
-        <v>286</v>
-      </c>
       <c r="AW61" t="s">
         <v>554</v>
       </c>
@@ -11777,9 +11633,6 @@
       <c r="AS62">
         <v>340</v>
       </c>
-      <c r="AV62" t="s">
-        <v>286</v>
-      </c>
       <c r="AW62" t="s">
         <v>560</v>
       </c>
@@ -11831,9 +11684,7 @@
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
-      <c r="S63" s="1" t="s">
-        <v>577</v>
-      </c>
+      <c r="S63" s="1"/>
       <c r="T63" t="s">
         <v>30</v>
       </c>
@@ -11888,9 +11739,6 @@
       </c>
       <c r="AS63">
         <v>340</v>
-      </c>
-      <c r="AV63" t="s">
-        <v>286</v>
       </c>
       <c r="AW63" t="s">
         <v>560</v>
@@ -15142,9 +14990,6 @@
       <c r="AS93">
         <v>150</v>
       </c>
-      <c r="AV93" t="s">
-        <v>286</v>
-      </c>
       <c r="AW93" t="s">
         <v>157</v>
       </c>
@@ -15258,9 +15103,6 @@
       <c r="AS94">
         <v>150</v>
       </c>
-      <c r="AV94" t="s">
-        <v>286</v>
-      </c>
       <c r="AW94" t="s">
         <v>704</v>
       </c>
@@ -15371,9 +15213,6 @@
       <c r="AS95">
         <v>150</v>
       </c>
-      <c r="AV95" t="s">
-        <v>286</v>
-      </c>
       <c r="AW95" t="s">
         <v>157</v>
       </c>
@@ -15484,9 +15323,6 @@
       <c r="AS96">
         <v>150</v>
       </c>
-      <c r="AV96" t="s">
-        <v>286</v>
-      </c>
       <c r="AW96" t="s">
         <v>157</v>
       </c>
@@ -15597,9 +15433,6 @@
       <c r="AS97">
         <v>150</v>
       </c>
-      <c r="AV97" t="s">
-        <v>286</v>
-      </c>
       <c r="AW97" t="s">
         <v>157</v>
       </c>
@@ -15713,9 +15546,6 @@
       <c r="AS98">
         <v>150</v>
       </c>
-      <c r="AV98" t="s">
-        <v>286</v>
-      </c>
       <c r="AW98" t="s">
         <v>704</v>
       </c>
@@ -15825,9 +15655,6 @@
       </c>
       <c r="AS99">
         <v>250</v>
-      </c>
-      <c r="AV99" t="s">
-        <v>286</v>
       </c>
       <c r="AW99" t="s">
         <v>157</v>
@@ -15936,9 +15763,6 @@
       <c r="AU100">
         <v>50</v>
       </c>
-      <c r="AV100" t="s">
-        <v>286</v>
-      </c>
       <c r="AW100" t="s">
         <v>725</v>
       </c>
@@ -16048,9 +15872,6 @@
       <c r="AU101">
         <v>50</v>
       </c>
-      <c r="AV101" t="s">
-        <v>286</v>
-      </c>
       <c r="AW101" t="s">
         <v>731</v>
       </c>
@@ -16175,9 +15996,6 @@
       </c>
       <c r="AU102">
         <v>50</v>
-      </c>
-      <c r="AV102" t="s">
-        <v>286</v>
       </c>
       <c r="AW102" t="s">
         <v>741</v>
@@ -16759,9 +16577,6 @@
       <c r="AU107">
         <v>100</v>
       </c>
-      <c r="AV107" t="s">
-        <v>286</v>
-      </c>
       <c r="AW107" t="s">
         <v>772</v>
       </c>
@@ -16869,9 +16684,6 @@
       <c r="AU108">
         <v>100</v>
       </c>
-      <c r="AV108" t="s">
-        <v>286</v>
-      </c>
       <c r="AW108" t="s">
         <v>772</v>
       </c>
@@ -17205,9 +17017,6 @@
       <c r="AU111">
         <v>1000</v>
       </c>
-      <c r="AV111" t="s">
-        <v>286</v>
-      </c>
       <c r="AW111" t="s">
         <v>796</v>
       </c>
@@ -17317,9 +17126,6 @@
       <c r="AU112">
         <v>1500</v>
       </c>
-      <c r="AV112" t="s">
-        <v>286</v>
-      </c>
       <c r="AW112" t="s">
         <v>796</v>
       </c>
@@ -17429,9 +17235,6 @@
       <c r="AU113">
         <v>50</v>
       </c>
-      <c r="AV113" t="s">
-        <v>286</v>
-      </c>
       <c r="AW113" t="s">
         <v>808</v>
       </c>
@@ -17541,9 +17344,6 @@
       <c r="AU114">
         <v>250</v>
       </c>
-      <c r="AV114" t="s">
-        <v>286</v>
-      </c>
       <c r="AW114" t="s">
         <v>808</v>
       </c>
@@ -17653,9 +17453,6 @@
       <c r="AU115">
         <v>1000</v>
       </c>
-      <c r="AV115" t="s">
-        <v>286</v>
-      </c>
       <c r="AW115" t="s">
         <v>808</v>
       </c>
@@ -18213,9 +18010,6 @@
       <c r="AJ120">
         <v>10</v>
       </c>
-      <c r="AV120" t="s">
-        <v>286</v>
-      </c>
       <c r="AW120" t="s">
         <v>851</v>
       </c>
@@ -18299,9 +18093,6 @@
       <c r="AJ121">
         <v>10</v>
       </c>
-      <c r="AV121" t="s">
-        <v>286</v>
-      </c>
       <c r="AW121" t="s">
         <v>851</v>
       </c>
@@ -18385,9 +18176,6 @@
       <c r="AJ122">
         <v>25</v>
       </c>
-      <c r="AV122" t="s">
-        <v>286</v>
-      </c>
       <c r="AW122" t="s">
         <v>851</v>
       </c>
@@ -18473,9 +18261,6 @@
       <c r="AJ123">
         <v>10</v>
       </c>
-      <c r="AV123" t="s">
-        <v>286</v>
-      </c>
       <c r="AW123" t="s">
         <v>863</v>
       </c>
@@ -18561,9 +18346,6 @@
       <c r="AJ124">
         <v>10</v>
       </c>
-      <c r="AV124" t="s">
-        <v>286</v>
-      </c>
       <c r="AW124" t="s">
         <v>863</v>
       </c>
@@ -18647,9 +18429,6 @@
       <c r="AJ125">
         <v>10</v>
       </c>
-      <c r="AV125" t="s">
-        <v>286</v>
-      </c>
       <c r="AW125" t="s">
         <v>851</v>
       </c>
@@ -18738,9 +18517,6 @@
       <c r="AS126">
         <v>300000</v>
       </c>
-      <c r="AV126" t="s">
-        <v>286</v>
-      </c>
       <c r="AW126" t="s">
         <v>878</v>
       </c>
@@ -18829,9 +18605,6 @@
       <c r="AS127">
         <v>300000</v>
       </c>
-      <c r="AV127" t="s">
-        <v>286</v>
-      </c>
       <c r="AW127" t="s">
         <v>878</v>
       </c>
@@ -18920,9 +18693,6 @@
       <c r="AS128">
         <v>300000</v>
       </c>
-      <c r="AV128" t="s">
-        <v>286</v>
-      </c>
       <c r="AW128" t="s">
         <v>878</v>
       </c>
@@ -19008,9 +18778,6 @@
       <c r="AJ129">
         <v>100</v>
       </c>
-      <c r="AV129" t="s">
-        <v>286</v>
-      </c>
       <c r="AW129" t="s">
         <v>878</v>
       </c>
@@ -19094,9 +18861,6 @@
       <c r="AJ130">
         <v>10</v>
       </c>
-      <c r="AV130" t="s">
-        <v>286</v>
-      </c>
       <c r="AW130" t="s">
         <v>878</v>
       </c>
@@ -19180,9 +18944,6 @@
       <c r="AJ131">
         <v>100</v>
       </c>
-      <c r="AV131" t="s">
-        <v>286</v>
-      </c>
       <c r="AW131" t="s">
         <v>896</v>
       </c>
@@ -19266,9 +19027,6 @@
       <c r="AJ132">
         <v>10</v>
       </c>
-      <c r="AV132" t="s">
-        <v>286</v>
-      </c>
       <c r="AW132" t="s">
         <v>896</v>
       </c>
@@ -19352,9 +19110,6 @@
       <c r="AJ133">
         <v>100</v>
       </c>
-      <c r="AV133" t="s">
-        <v>286</v>
-      </c>
       <c r="AW133" t="s">
         <v>878</v>
       </c>
@@ -19438,9 +19193,6 @@
       <c r="AJ134">
         <v>400</v>
       </c>
-      <c r="AV134" t="s">
-        <v>286</v>
-      </c>
       <c r="AX134" s="1" t="s">
         <v>909</v>
       </c>
@@ -19521,9 +19273,6 @@
       <c r="AJ135">
         <v>400</v>
       </c>
-      <c r="AV135" t="s">
-        <v>286</v>
-      </c>
       <c r="AX135" s="1" t="s">
         <v>913</v>
       </c>
@@ -19613,9 +19362,6 @@
       <c r="AS136">
         <v>800000</v>
       </c>
-      <c r="AV136" t="s">
-        <v>286</v>
-      </c>
       <c r="AW136" t="s">
         <v>918</v>
       </c>
@@ -19710,9 +19456,6 @@
       <c r="AS137">
         <v>800000</v>
       </c>
-      <c r="AV137" t="s">
-        <v>286</v>
-      </c>
       <c r="AW137" t="s">
         <v>918</v>
       </c>
@@ -19807,9 +19550,6 @@
       <c r="AS138">
         <v>800000</v>
       </c>
-      <c r="AV138" t="s">
-        <v>286</v>
-      </c>
       <c r="AW138" t="s">
         <v>918</v>
       </c>
@@ -19904,9 +19644,6 @@
       <c r="AS139">
         <v>800000</v>
       </c>
-      <c r="AV139" t="s">
-        <v>286</v>
-      </c>
       <c r="AW139" t="s">
         <v>918</v>
       </c>
@@ -19995,9 +19732,6 @@
       <c r="AS140">
         <v>4800000</v>
       </c>
-      <c r="AV140" t="s">
-        <v>286</v>
-      </c>
       <c r="AX140" s="1" t="s">
         <v>939</v>
       </c>
@@ -20079,9 +19813,6 @@
       <c r="AS141">
         <v>4800000</v>
       </c>
-      <c r="AV141" t="s">
-        <v>286</v>
-      </c>
       <c r="AX141" s="1" t="s">
         <v>942</v>
       </c>
@@ -20166,9 +19897,6 @@
       <c r="AS142">
         <v>2400000</v>
       </c>
-      <c r="AV142" t="s">
-        <v>286</v>
-      </c>
       <c r="AX142" s="1" t="s">
         <v>946</v>
       </c>
@@ -20255,9 +19983,6 @@
       <c r="AS143">
         <v>2400000</v>
       </c>
-      <c r="AV143" t="s">
-        <v>286</v>
-      </c>
       <c r="AX143" s="1" t="s">
         <v>950</v>
       </c>
@@ -20341,9 +20066,6 @@
       <c r="AS144">
         <v>2400000</v>
       </c>
-      <c r="AV144" t="s">
-        <v>286</v>
-      </c>
       <c r="AX144" s="1" t="s">
         <v>954</v>
       </c>
@@ -20422,9 +20144,6 @@
       <c r="AS145">
         <v>7200000</v>
       </c>
-      <c r="AV145" t="s">
-        <v>286</v>
-      </c>
       <c r="AX145" s="1" t="s">
         <v>958</v>
       </c>
@@ -20508,9 +20227,6 @@
       <c r="AS146">
         <v>800000</v>
       </c>
-      <c r="AV146" t="s">
-        <v>286</v>
-      </c>
       <c r="AW146" t="s">
         <v>964</v>
       </c>
@@ -20599,9 +20315,6 @@
       <c r="AS147">
         <v>800000</v>
       </c>
-      <c r="AV147" t="s">
-        <v>286</v>
-      </c>
       <c r="AW147" t="s">
         <v>964</v>
       </c>
@@ -20696,9 +20409,6 @@
       <c r="AS148">
         <v>28800000</v>
       </c>
-      <c r="AV148" t="s">
-        <v>286</v>
-      </c>
       <c r="AW148" t="s">
         <v>975</v>
       </c>
@@ -20793,9 +20503,6 @@
       <c r="AS149">
         <v>57600000</v>
       </c>
-      <c r="AV149" t="s">
-        <v>286</v>
-      </c>
       <c r="AW149" t="s">
         <v>975</v>
       </c>
@@ -20899,9 +20606,6 @@
       <c r="AR150" t="s">
         <v>68</v>
       </c>
-      <c r="AV150" t="s">
-        <v>286</v>
-      </c>
       <c r="AW150" t="s">
         <v>987</v>
       </c>
@@ -20988,9 +20692,6 @@
       <c r="AR151" t="s">
         <v>68</v>
       </c>
-      <c r="AV151" t="s">
-        <v>286</v>
-      </c>
       <c r="AW151" t="s">
         <v>994</v>
       </c>
@@ -21077,9 +20778,6 @@
       <c r="AR152" t="s">
         <v>68</v>
       </c>
-      <c r="AV152" t="s">
-        <v>286</v>
-      </c>
       <c r="AW152" t="s">
         <v>994</v>
       </c>
@@ -21368,9 +21066,6 @@
       <c r="AR155" t="s">
         <v>68</v>
       </c>
-      <c r="AV155" t="s">
-        <v>286</v>
-      </c>
       <c r="AW155" t="s">
         <v>1014</v>
       </c>
@@ -21463,9 +21158,6 @@
       <c r="AR156" t="s">
         <v>68</v>
       </c>
-      <c r="AV156" t="s">
-        <v>286</v>
-      </c>
       <c r="AW156" t="s">
         <v>1014</v>
       </c>
@@ -21555,9 +21247,6 @@
       <c r="AN157">
         <v>20</v>
       </c>
-      <c r="AV157" t="s">
-        <v>286</v>
-      </c>
       <c r="AW157" t="s">
         <v>1024</v>
       </c>
@@ -21649,9 +21338,6 @@
       <c r="AN158">
         <v>10</v>
       </c>
-      <c r="AV158" t="s">
-        <v>286</v>
-      </c>
       <c r="AW158" t="s">
         <v>1024</v>
       </c>
@@ -21743,9 +21429,6 @@
       <c r="AN159">
         <v>8</v>
       </c>
-      <c r="AV159" t="s">
-        <v>286</v>
-      </c>
       <c r="AW159" t="s">
         <v>1024</v>
       </c>
@@ -21837,9 +21520,6 @@
       <c r="AN160">
         <v>4</v>
       </c>
-      <c r="AV160" t="s">
-        <v>286</v>
-      </c>
       <c r="AW160" t="s">
         <v>1024</v>
       </c>
@@ -21931,9 +21611,6 @@
       <c r="AN161">
         <v>2</v>
       </c>
-      <c r="AV161" t="s">
-        <v>286</v>
-      </c>
       <c r="AW161" t="s">
         <v>1024</v>
       </c>
@@ -22028,9 +21705,6 @@
       <c r="AS162">
         <v>3600000</v>
       </c>
-      <c r="AV162" t="s">
-        <v>286</v>
-      </c>
       <c r="AW162" t="s">
         <v>1024</v>
       </c>
@@ -22125,9 +21799,6 @@
       <c r="AS163">
         <v>800000</v>
       </c>
-      <c r="AV163" t="s">
-        <v>286</v>
-      </c>
       <c r="AW163" t="s">
         <v>1024</v>
       </c>
@@ -22219,9 +21890,6 @@
       <c r="AN164">
         <v>8</v>
       </c>
-      <c r="AV164" t="s">
-        <v>286</v>
-      </c>
       <c r="AW164" t="s">
         <v>1024</v>
       </c>
@@ -22313,9 +21981,6 @@
       <c r="AN165">
         <v>4</v>
       </c>
-      <c r="AV165" t="s">
-        <v>286</v>
-      </c>
       <c r="AW165" t="s">
         <v>1024</v>
       </c>
@@ -22397,9 +22062,6 @@
       </c>
       <c r="AN166">
         <v>0</v>
-      </c>
-      <c r="AV166" t="s">
-        <v>286</v>
       </c>
       <c r="AX166" s="1" t="s">
         <v>1063</v>

--- a/data/catalog/routing.xlsx
+++ b/data/catalog/routing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5866" uniqueCount="1461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5867" uniqueCount="1461">
   <si>
     <t>family</t>
   </si>
@@ -2756,7 +2756,7 @@
     <t>2031-11-30</t>
   </si>
   <si>
-    <t>Cisco'nun önerdiği yedek: C8111-C-G2-MX (Meraki yönetimli Catalyst 8111-G2).</t>
+    <t>Cisco'nun önerdiği yedek: Meraki yönetimli Catalyst 8111 G2 yönlendirici (henüz kataloğa eklenmedi).</t>
   </si>
   <si>
     <t>https://www.cisco.com/c/en/us/products/collateral/security/meraki-cloud-managed-security-appliances/mx67c-mx68cw-eol.pdf</t>
@@ -2837,7 +2837,7 @@
     <t>Meraki MX68 cloud-managed security appliance (end of sale announced): 3 WAN ports (up to 1G); stateful firewall 700 Mbps, next-generation firewall (NGFW) 400 Mbps. Built-in cellular (LTE/5G) modem. Supports SD-WAN. Has ports that can supply PoE.</t>
   </si>
   <si>
-    <t>Cisco'nun önerdiği yedek: C8121-CW-G2-MX (Meraki yönetimli Catalyst 8121-G2).</t>
+    <t>Cisco'nun önerdiği yedek: Meraki yönetimli Catalyst 8121 G2 yönlendirici (henüz kataloğa eklenmedi).</t>
   </si>
   <si>
     <t>wireless, lte, poe, cryptography, ngfw_capable, ips, ids, advanced_malware_protection, url_filtering</t>
@@ -3161,7 +3161,7 @@
     <t>2029-09-04</t>
   </si>
   <si>
-    <t>Yedek olarak Z4 / Z4C öneriliyor; ikisi de henüz yayınlanmadı (veri eksik).</t>
+    <t>Yedek olarak yeni nesil Z-Series geçidi öneriliyor (henüz kataloğa eklenmedi).</t>
   </si>
   <si>
     <t>https://documentation.meraki.com/@api/deki/files/24994/Z3-HW_EOS_Notice_(1).pdf?revision=1</t>
@@ -3200,7 +3200,10 @@
     <t>Meraki Z-Series teleworker gateway (end of sale): 2 WAN ports (up to 1G); stateful firewall 100 Mbps. Built-in cellular (LTE/5G) modem. Supports SD-WAN. Has ports that can supply PoE.</t>
   </si>
   <si>
-    <t>Yedek olarak Z4C öneriliyor; henüz yayınlanmadı (veri eksik). Z3C-HW-WW için son sipariş 11 Şubat 2024'tü.</t>
+    <t>Z4C</t>
+  </si>
+  <si>
+    <t>Z3C-HW-WW için son sipariş 11 Şubat 2024'tü.</t>
   </si>
   <si>
     <t>https://documentation.meraki.com/@api/deki/files/24993/Z3C-HW-NA.pdf?revision=1</t>
@@ -3239,9 +3242,6 @@
     <t>The Z4 datasheet page could not be read (the specs are not in the page text); Z4C was read and Z4 is not assumed to match it.</t>
   </si>
   <si>
-    <t>Z4C</t>
-  </si>
-  <si>
     <t>Meraki Z-Series uzaktan çalışan geçidi: 2 WAN portu (en fazla 1G); durum izlemeli güvenlik duvarı 500 Mbps, güvenlik 300 Mbps. Dahili hücresel (LTE/5G) modem. SD-WAN destekler. PoE verebilen portları var.</t>
   </si>
   <si>
@@ -4388,10 +4388,10 @@
     <t>Meraki MX95: a firewall and SD-WAN appliance managed from the Meraki dashboard, for large branches and small campuses.</t>
   </si>
   <si>
-    <t>Meraki Z-Series: uzaktan çalışanlar için küçük, bulut yönetimli güvenlik geçidi; evden şirket ağına VPN kurar. Burada Z4C ile satışı sona eren Z3 modelleri listelenir; Z4 henüz eklenmedi.</t>
-  </si>
-  <si>
-    <t>Meraki Z-Series: small cloud-managed security gateways for teleworkers that build a VPN from home to the company network. Listed here are the Z4C and the Z3 models, which are end of sale; the Z4 is not added yet.</t>
+    <t>Meraki Z-Series: uzaktan çalışanlar için küçük, bulut yönetimli güvenlik geçidi; evden şirket ağına VPN kurar. Burada Z4C ile satışı sona eren Z3 modelleri listelenir; diğer Z-Series modelleri henüz eklenmedi.</t>
+  </si>
+  <si>
+    <t>Meraki Z-Series: small cloud-managed security gateways for teleworkers that build a VPN from home to the company network. Listed here are the Z4C and the Z3 models, which are end of sale; the other Z-Series models are not added yet.</t>
   </si>
   <si>
     <t>Meraki vMX: AWS, Azure, Google Cloud ve Alibaba Cloud'da çalışan sanal MX; bulut kaynaklarını Meraki SD-WAN ağına bağlar. S, M ve L boyutları vardır.</t>
@@ -21134,12 +21134,14 @@
       <c r="O117" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="P117" s="1"/>
+      <c r="P117" s="1" t="s">
+        <v>1061</v>
+      </c>
       <c r="Q117" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="S117" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="T117" t="s">
         <v>55</v>
@@ -21159,7 +21161,7 @@
         <v>1052</v>
       </c>
       <c r="AA117" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="AB117" s="1" t="s">
         <v>345</v>
@@ -21218,25 +21220,25 @@
         <v>291</v>
       </c>
       <c r="AZ117" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="BA117" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="BB117" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="BC117" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="BD117" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="BE117" s="1"/>
     </row>
     <row r="118" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B118" t="s">
         <v>76</v>
@@ -21251,10 +21253,10 @@
         <v>28</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -21274,7 +21276,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
       <c r="Z118" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
@@ -21333,24 +21335,24 @@
         <v>1053</v>
       </c>
       <c r="BA118" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="BB118" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="BC118" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="BD118" s="1" t="s">
         <v>1057</v>
       </c>
       <c r="BE118" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="119" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>1074</v>
+        <v>1061</v>
       </c>
       <c r="B119" t="s">
         <v>76</v>
@@ -21365,10 +21367,10 @@
         <v>28</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>1074</v>
+        <v>1061</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>1074</v>
+        <v>1061</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>1075</v>
@@ -21471,7 +21473,7 @@
         <v>291</v>
       </c>
       <c r="AZ119" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="BA119" s="1" t="s">
         <v>1080</v>
@@ -21483,7 +21485,7 @@
         <v>1082</v>
       </c>
       <c r="BD119" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="BE119" s="1"/>
     </row>

--- a/data/catalog/routing.xlsx
+++ b/data/catalog/routing.xlsx
@@ -3143,7 +3143,7 @@
     <t>Licence required: every Z-Series device needs a Meraki licence.</t>
   </si>
   <si>
-    <t>https://meraki.cisco.com/product-collateral/z-series-datasheet/?file</t>
+    <t>https://documentation.meraki.com/SASE_and_SD-WAN/Z-Series_Teleworker_Gateways</t>
   </si>
   <si>
     <t>wireless, poe, cryptography, ngfw_capable</t>
